--- a/data/trans_orig/P71_R2-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P71_R2-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según dificultad para llegar a fin de mes en 2007</t>
+          <t>Población según dificultad para llegar a fin de mes en 2007 (tasa de respuesta: 98,33%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>58540</t>
+          <t>58913</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>91647</t>
+          <t>90708</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>43455</t>
+          <t>44131</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>72315</t>
+          <t>72221</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>109495</t>
+          <t>107852</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>152971</t>
+          <t>153310</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,68%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>232032</t>
+          <t>232819</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>288710</t>
+          <t>287075</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>257181</t>
+          <t>255432</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>314492</t>
+          <t>315402</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>506569</t>
+          <t>507523</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>587824</t>
+          <t>590494</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,74%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>346957</t>
+          <t>343540</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>406442</t>
+          <t>405148</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>393591</t>
+          <t>392350</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>461732</t>
+          <t>460115</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>753958</t>
+          <t>755202</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>845949</t>
+          <t>844947</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>36,84%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>275674</t>
+          <t>272195</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>335133</t>
+          <t>333262</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>482695</t>
+          <t>482314</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>548500</t>
+          <t>552293</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>43,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>770595</t>
+          <t>771554</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>863394</t>
+          <t>862116</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>37,59%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>168992</t>
+          <t>168027</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>221192</t>
+          <t>220762</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>129073</t>
+          <t>130278</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>175940</t>
+          <t>176321</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>309906</t>
+          <t>312462</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>380632</t>
+          <t>379558</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,73%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>607686</t>
+          <t>610135</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>686951</t>
+          <t>690620</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>476738</t>
+          <t>482417</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>550767</t>
+          <t>556193</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1109853</t>
+          <t>1110385</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1216469</t>
+          <t>1219719</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>37,7%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>549876</t>
+          <t>553522</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>632336</t>
+          <t>627746</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>505521</t>
+          <t>503754</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>578154</t>
+          <t>580875</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>37,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1074362</t>
+          <t>1077436</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1192448</t>
+          <t>1191156</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>36,81%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>217490</t>
+          <t>214094</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>274993</t>
+          <t>272942</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>320751</t>
+          <t>318012</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>387494</t>
+          <t>385215</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>549446</t>
+          <t>552637</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>637779</t>
+          <t>644890</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,93%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>158409</t>
+          <t>159286</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>203748</t>
+          <t>206634</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>37,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>113469</t>
+          <t>113028</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>152440</t>
+          <t>152503</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>284075</t>
+          <t>285920</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>344106</t>
+          <t>343851</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>33,83%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>190865</t>
+          <t>191010</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>238443</t>
+          <t>238220</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>34,94%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>43,62%</t>
+          <t>43,57%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>170592</t>
+          <t>169738</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>211782</t>
+          <t>213299</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>45,1%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>373880</t>
+          <t>374189</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>436872</t>
+          <t>441234</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>42,99%</t>
+          <t>43,41%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>96123</t>
+          <t>95069</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>136328</t>
+          <t>133375</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>73362</t>
+          <t>72743</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>107476</t>
+          <t>108748</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>176927</t>
+          <t>178877</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>230560</t>
+          <t>230806</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,71%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>26995</t>
+          <t>27003</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>52582</t>
+          <t>51938</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>43939</t>
+          <t>42708</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>73811</t>
+          <t>72687</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>76028</t>
+          <t>75279</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>115360</t>
+          <t>116377</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,45%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>411386</t>
+          <t>411848</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>488922</t>
+          <t>492353</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>306911</t>
+          <t>304993</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>377855</t>
+          <t>376959</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>734726</t>
+          <t>734965</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>842184</t>
+          <t>841308</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,85%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1073923</t>
+          <t>1063806</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1181036</t>
+          <t>1177014</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>944363</t>
+          <t>940337</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1048545</t>
+          <t>1046412</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2037523</t>
+          <t>2044277</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2195403</t>
+          <t>2191729</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>33,48%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1024300</t>
+          <t>1020437</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1135660</t>
+          <t>1134335</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>31,58%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>999325</t>
+          <t>1002253</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1109321</t>
+          <t>1112961</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2064885</t>
+          <t>2052357</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2223075</t>
+          <t>2208030</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>33,73%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>536405</t>
+          <t>542936</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>626782</t>
+          <t>627470</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>873035</t>
+          <t>873730</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>977713</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1429935</t>
+          <t>1443179</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1569869</t>
+          <t>1577379</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>24,1%</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3045,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según dificultad para llegar a fin de mes en 2012</t>
+          <t>Población según dificultad para llegar a fin de mes en 2012 (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3240,12 +3240,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>62832</t>
+          <t>62937</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>98705</t>
+          <t>99527</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3255,12 +3255,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3275,12 +3275,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>84847</t>
+          <t>84090</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>123678</t>
+          <t>125008</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3310,12 +3310,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>157792</t>
+          <t>154952</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>209799</t>
+          <t>210158</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3325,12 +3325,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,14%</t>
         </is>
       </c>
     </row>
@@ -3353,12 +3353,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>186666</t>
+          <t>185930</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>241281</t>
+          <t>240985</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3388,12 +3388,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>290454</t>
+          <t>290632</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>353437</t>
+          <t>351762</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3423,12 +3423,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>496416</t>
+          <t>491361</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>578076</t>
+          <t>575690</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,05%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>253746</t>
+          <t>254673</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>310433</t>
+          <t>314551</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>386881</t>
+          <t>389094</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>457500</t>
+          <t>457751</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>34,41%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>658612</t>
+          <t>661015</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>751444</t>
+          <t>748884</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,58%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>364392</t>
+          <t>361493</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>425762</t>
+          <t>424807</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>43,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>447135</t>
+          <t>449906</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>519306</t>
+          <t>517913</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>38,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>831869</t>
+          <t>826598</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>926416</t>
+          <t>923018</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,31%</t>
+          <t>40,16%</t>
         </is>
       </c>
     </row>
@@ -3809,12 +3809,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>224665</t>
+          <t>225341</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>289264</t>
+          <t>286081</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>172320</t>
+          <t>174580</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>229550</t>
+          <t>229731</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>417931</t>
+          <t>417123</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>498756</t>
+          <t>499922</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,48%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>463953</t>
+          <t>465090</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>541678</t>
+          <t>543966</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>385400</t>
+          <t>381430</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>458441</t>
+          <t>458607</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>869837</t>
+          <t>861836</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>973955</t>
+          <t>971688</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,2%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>564320</t>
+          <t>567097</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>652560</t>
+          <t>651262</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>524995</t>
+          <t>523326</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>605424</t>
+          <t>606866</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1118526</t>
+          <t>1122215</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1233357</t>
+          <t>1237280</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>33,36%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>547948</t>
+          <t>549366</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>632296</t>
+          <t>631463</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>528110</t>
+          <t>526491</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>608084</t>
+          <t>610175</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1094335</t>
+          <t>1100815</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1210694</t>
+          <t>1215731</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,77%</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4378,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>143033</t>
+          <t>142746</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>188613</t>
+          <t>188862</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>39,69%</t>
+          <t>39,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>127443</t>
+          <t>127345</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>169921</t>
+          <t>170254</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>285189</t>
+          <t>285800</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>346697</t>
+          <t>348606</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>37,37%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>147389</t>
+          <t>144747</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>191137</t>
+          <t>186816</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>116039</t>
+          <t>117092</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>156965</t>
+          <t>158793</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>274680</t>
+          <t>272763</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>333476</t>
+          <t>334792</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>35,89%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>67152</t>
+          <t>66914</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>102981</t>
+          <t>100912</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>88866</t>
+          <t>86104</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>125657</t>
+          <t>125452</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>161664</t>
+          <t>163485</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>215364</t>
+          <t>217347</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,3%</t>
         </is>
       </c>
     </row>
@@ -4717,12 +4717,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>43409</t>
+          <t>44713</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>75176</t>
+          <t>74502</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>53107</t>
+          <t>53327</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>84120</t>
+          <t>84871</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4767,12 +4767,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>105166</t>
+          <t>104439</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>150104</t>
+          <t>149917</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,07%</t>
         </is>
       </c>
     </row>
@@ -4947,12 +4947,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>461034</t>
+          <t>459194</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>548047</t>
+          <t>549535</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4962,12 +4962,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>411257</t>
+          <t>407897</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>496618</t>
+          <t>490977</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4997,12 +4997,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>896801</t>
+          <t>895086</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1022152</t>
+          <t>1012895</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5032,12 +5032,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,59%</t>
         </is>
       </c>
     </row>
@@ -5060,12 +5060,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>831732</t>
+          <t>832475</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>942591</t>
+          <t>937003</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>822449</t>
+          <t>822890</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>927138</t>
+          <t>931305</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1693896</t>
+          <t>1685419</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1836638</t>
+          <t>1832043</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,4%</t>
         </is>
       </c>
     </row>
@@ -5173,12 +5173,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>912647</t>
+          <t>920732</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1026299</t>
+          <t>1034466</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1035221</t>
+          <t>1039922</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1148765</t>
+          <t>1149952</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5223,12 +5223,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1985691</t>
+          <t>1991949</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2139973</t>
+          <t>2150582</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5258,12 +5258,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>30,98%</t>
         </is>
       </c>
     </row>
@@ -5286,12 +5286,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>986910</t>
+          <t>990155</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1097969</t>
+          <t>1104671</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1062526</t>
+          <t>1062824</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1174305</t>
+          <t>1180451</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5341,7 +5341,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2080255</t>
+          <t>2081987</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2241161</t>
+          <t>2236096</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5371,12 +5371,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>32,22%</t>
         </is>
       </c>
     </row>
@@ -5552,7 +5552,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según dificultad para llegar a fin de mes en 2016</t>
+          <t>Población según dificultad para llegar a fin de mes en 2016 (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5747,12 +5747,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>60322</t>
+          <t>59209</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>91990</t>
+          <t>91641</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5762,12 +5762,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>63237</t>
+          <t>62722</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>101028</t>
+          <t>99756</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5797,12 +5797,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>132126</t>
+          <t>132246</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>181462</t>
+          <t>182300</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5832,12 +5832,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,5%</t>
         </is>
       </c>
     </row>
@@ -5860,12 +5860,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>104186</t>
+          <t>106513</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>142924</t>
+          <t>146210</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5875,12 +5875,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5895,12 +5895,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>146774</t>
+          <t>146253</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>195357</t>
+          <t>195287</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5910,7 +5910,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>264517</t>
+          <t>259005</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>328725</t>
+          <t>328435</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5945,12 +5945,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,92%</t>
         </is>
       </c>
     </row>
@@ -5973,12 +5973,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>169696</t>
+          <t>169156</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>217102</t>
+          <t>217371</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6008,12 +6008,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>219820</t>
+          <t>218810</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>277417</t>
+          <t>272916</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6023,12 +6023,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>399851</t>
+          <t>403429</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>471918</t>
+          <t>477823</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6058,12 +6058,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>27,53%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>329165</t>
+          <t>329806</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>380755</t>
+          <t>384303</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>50,95%</t>
+          <t>51,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>457343</t>
+          <t>460805</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>524259</t>
+          <t>523781</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>46,27%</t>
+          <t>46,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>53,04%</t>
+          <t>52,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>808052</t>
+          <t>805045</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>890837</t>
+          <t>890663</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>46,55%</t>
+          <t>46,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>51,32%</t>
+          <t>51,31%</t>
         </is>
       </c>
     </row>
@@ -6316,12 +6316,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>217757</t>
+          <t>218906</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>281243</t>
+          <t>277194</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6331,12 +6331,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>207094</t>
+          <t>210558</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>267400</t>
+          <t>269096</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6366,12 +6366,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>439778</t>
+          <t>445791</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>530129</t>
+          <t>528039</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,08%</t>
         </is>
       </c>
     </row>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>473370</t>
+          <t>467478</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>553815</t>
+          <t>547699</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>382488</t>
+          <t>385251</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>456657</t>
+          <t>458778</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>872319</t>
+          <t>879473</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>979652</t>
+          <t>988129</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6514,12 +6514,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,48%</t>
         </is>
       </c>
     </row>
@@ -6542,12 +6542,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>555312</t>
+          <t>555700</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>634917</t>
+          <t>638282</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6557,12 +6557,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>592877</t>
+          <t>592377</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>677508</t>
+          <t>676185</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6592,12 +6592,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6612,12 +6612,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1173743</t>
+          <t>1170268</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1292089</t>
+          <t>1286848</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6627,12 +6627,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>31,88%</t>
         </is>
       </c>
     </row>
@@ -6655,12 +6655,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>664721</t>
+          <t>659751</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>751674</t>
+          <t>751421</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6670,12 +6670,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>643680</t>
+          <t>647347</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>729360</t>
+          <t>731035</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>36,96%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1332757</t>
+          <t>1327479</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1458875</t>
+          <t>1459300</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>36,16%</t>
         </is>
       </c>
     </row>
@@ -6885,12 +6885,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>159065</t>
+          <t>161268</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>206412</t>
+          <t>208629</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6900,82 +6900,82 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>29,59%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>38,28%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>169581</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>147624</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>190913</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>30,94%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>26,94%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>34,83%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>351110</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>319044</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>384509</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>32,12%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>29,19%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>37,88%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>169581</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>147288</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>191230</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>30,94%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>26,87%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>34,89%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>321</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>351110</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>321793</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>383880</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>32,12%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>29,44%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>35,18%</t>
         </is>
       </c>
     </row>
@@ -6998,12 +6998,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>161830</t>
+          <t>159880</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>207773</t>
+          <t>205415</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7013,12 +7013,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7033,12 +7033,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>153896</t>
+          <t>154876</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>197574</t>
+          <t>198901</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7068,12 +7068,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>329158</t>
+          <t>329804</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>393473</t>
+          <t>390983</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7083,12 +7083,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>35,77%</t>
         </is>
       </c>
     </row>
@@ -7111,12 +7111,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>98142</t>
+          <t>98773</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>138590</t>
+          <t>139272</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7126,12 +7126,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7146,12 +7146,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>105898</t>
+          <t>105999</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>146727</t>
+          <t>147795</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7161,12 +7161,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>218069</t>
+          <t>216560</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>275730</t>
+          <t>272483</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7196,12 +7196,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>24,93%</t>
         </is>
       </c>
     </row>
@@ -7224,12 +7224,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>44663</t>
+          <t>44998</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>76382</t>
+          <t>76176</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7239,12 +7239,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7259,12 +7259,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>62077</t>
+          <t>60957</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>94666</t>
+          <t>93692</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7274,12 +7274,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7294,12 +7294,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>114286</t>
+          <t>115871</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>158863</t>
+          <t>159996</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7309,12 +7309,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,64%</t>
         </is>
       </c>
     </row>
@@ -7454,12 +7454,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>463873</t>
+          <t>460609</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>551224</t>
+          <t>546080</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7469,12 +7469,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7489,12 +7489,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>445278</t>
+          <t>441665</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>531482</t>
+          <t>525107</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7504,12 +7504,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>928793</t>
+          <t>935336</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1046447</t>
+          <t>1054457</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7539,12 +7539,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,36%</t>
         </is>
       </c>
     </row>
@@ -7567,12 +7567,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>770201</t>
+          <t>763793</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>872035</t>
+          <t>870167</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7582,12 +7582,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7602,12 +7602,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>721188</t>
+          <t>715786</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>819908</t>
+          <t>816640</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7617,12 +7617,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7637,12 +7637,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1516920</t>
+          <t>1511521</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1655172</t>
+          <t>1650498</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7652,12 +7652,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,04%</t>
         </is>
       </c>
     </row>
@@ -7680,12 +7680,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>858699</t>
+          <t>859451</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>962954</t>
+          <t>963875</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7695,12 +7695,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7715,12 +7715,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>948448</t>
+          <t>951321</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1057997</t>
+          <t>1061907</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7730,12 +7730,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7750,12 +7750,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1838660</t>
+          <t>1844533</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1984389</t>
+          <t>1994552</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7765,12 +7765,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>29,05%</t>
         </is>
       </c>
     </row>
@@ -7793,12 +7793,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1063194</t>
+          <t>1062183</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1175195</t>
+          <t>1172666</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7808,12 +7808,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7828,12 +7828,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1200047</t>
+          <t>1197515</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1319981</t>
+          <t>1313839</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>34,07%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>37,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7863,12 +7863,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2297526</t>
+          <t>2292824</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2456657</t>
+          <t>2451188</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>35,71%</t>
         </is>
       </c>
     </row>
@@ -8059,7 +8059,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según dificultad para llegar a fin de mes en 2023</t>
+          <t>Población según dificultad para llegar a fin de mes en 2023 (tasa de respuesta: 98,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>74589</t>
+          <t>74764</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>105597</t>
+          <t>106853</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8269,12 +8269,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8289,12 +8289,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>75268</t>
+          <t>76148</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>102082</t>
+          <t>102662</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8324,12 +8324,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>156522</t>
+          <t>156437</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>199917</t>
+          <t>199612</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,0%</t>
         </is>
       </c>
     </row>
@@ -8367,12 +8367,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>83827</t>
+          <t>82698</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>116136</t>
+          <t>115912</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8382,12 +8382,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8402,12 +8402,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>139717</t>
+          <t>139712</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>172427</t>
+          <t>171402</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8422,7 +8422,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8437,12 +8437,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>230582</t>
+          <t>231922</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>277531</t>
+          <t>277287</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,22%</t>
         </is>
       </c>
     </row>
@@ -8480,12 +8480,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>161365</t>
+          <t>162244</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>200428</t>
+          <t>202564</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8495,12 +8495,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>40,14%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8515,12 +8515,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>277004</t>
+          <t>278256</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>317214</t>
+          <t>319930</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>43,06%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8550,12 +8550,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>451088</t>
+          <t>451372</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>509510</t>
+          <t>506548</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>40,6%</t>
         </is>
       </c>
     </row>
@@ -8593,12 +8593,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>118016</t>
+          <t>117461</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>154657</t>
+          <t>154640</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8608,12 +8608,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8628,12 +8628,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>183743</t>
+          <t>184883</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>224709</t>
+          <t>223749</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8663,12 +8663,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>310738</t>
+          <t>311551</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>364734</t>
+          <t>366728</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8678,12 +8678,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,39%</t>
         </is>
       </c>
     </row>
@@ -8823,12 +8823,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>312457</t>
+          <t>304871</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>541190</t>
+          <t>555106</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8838,12 +8838,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8853,17 +8853,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>621891</t>
+          <t>621892</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>443240</t>
+          <t>441116</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1090152</t>
+          <t>1073178</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>48,92%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8893,12 +8893,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>871288</t>
+          <t>887270</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1591999</t>
+          <t>1706293</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>38,29%</t>
         </is>
       </c>
     </row>
@@ -8936,12 +8936,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>457167</t>
+          <t>458582</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>768122</t>
+          <t>775872</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8951,12 +8951,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8966,17 +8966,17 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>583584</t>
+          <t>583585</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>398583</t>
+          <t>425499</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>669695</t>
+          <t>670918</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9006,12 +9006,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>997340</t>
+          <t>1015411</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1403371</t>
+          <t>1396403</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,34%</t>
         </is>
       </c>
     </row>
@@ -9049,12 +9049,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>674369</t>
+          <t>664526</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1321640</t>
+          <t>1339510</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9064,12 +9064,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>58,42%</t>
+          <t>59,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9084,12 +9084,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>433669</t>
+          <t>455988</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>703068</t>
+          <t>707809</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9099,12 +9099,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9119,12 +9119,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1231955</t>
+          <t>1229506</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1981139</t>
+          <t>2006585</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9134,12 +9134,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>45,03%</t>
         </is>
       </c>
     </row>
@@ -9162,12 +9162,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>188045</t>
+          <t>178814</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>311332</t>
+          <t>311258</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9177,7 +9177,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -9192,17 +9192,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>371002</t>
+          <t>371003</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>287690</t>
+          <t>283945</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>564842</t>
+          <t>577725</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9212,12 +9212,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9232,12 +9232,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>519129</t>
+          <t>518905</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>805441</t>
+          <t>852269</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9252,7 +9252,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>19,13%</t>
         </is>
       </c>
     </row>
@@ -9305,17 +9305,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2193571</t>
+          <t>2193572</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2193571</t>
+          <t>2193572</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2193571</t>
+          <t>2193572</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9392,12 +9392,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>303989</t>
+          <t>305612</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>359546</t>
+          <t>360524</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9407,12 +9407,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>47,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>55,93%</t>
+          <t>56,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>291231</t>
+          <t>292424</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>336518</t>
+          <t>338066</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>44,73%</t>
+          <t>44,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>51,68%</t>
+          <t>51,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>608717</t>
+          <t>611448</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>685402</t>
+          <t>683685</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>47,04%</t>
+          <t>47,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>52,97%</t>
+          <t>52,84%</t>
         </is>
       </c>
     </row>
@@ -9505,12 +9505,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>196372</t>
+          <t>194823</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>254290</t>
+          <t>252689</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9520,12 +9520,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>200275</t>
+          <t>202977</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>245708</t>
+          <t>244191</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9555,12 +9555,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>409544</t>
+          <t>410621</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>481974</t>
+          <t>481844</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9590,12 +9590,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>37,24%</t>
         </is>
       </c>
     </row>
@@ -9618,12 +9618,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>53618</t>
+          <t>54963</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>89783</t>
+          <t>91641</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9633,12 +9633,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>65648</t>
+          <t>65786</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>95043</t>
+          <t>94823</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9668,12 +9668,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9688,12 +9688,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>128417</t>
+          <t>127478</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>173381</t>
+          <t>174063</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9703,12 +9703,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,45%</t>
         </is>
       </c>
     </row>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10389</t>
+          <t>9928</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28678</t>
+          <t>29286</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9746,12 +9746,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9766,12 +9766,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>24462</t>
+          <t>25511</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>46587</t>
+          <t>45616</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9781,12 +9781,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9801,12 +9801,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>39188</t>
+          <t>38771</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>66830</t>
+          <t>65834</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9816,12 +9816,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,09%</t>
         </is>
       </c>
     </row>
@@ -9961,12 +9961,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>695491</t>
+          <t>687798</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>985398</t>
+          <t>981554</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9976,12 +9976,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>850598</t>
+          <t>852108</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1503947</t>
+          <t>1514074</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10011,12 +10011,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1721914</t>
+          <t>1690106</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2454464</t>
+          <t>2405023</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10046,12 +10046,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>34,37%</t>
         </is>
       </c>
     </row>
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>782253</t>
+          <t>744591</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1086964</t>
+          <t>1091345</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10089,12 +10089,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>804640</t>
+          <t>790086</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1048764</t>
+          <t>1045795</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10124,12 +10124,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1680669</t>
+          <t>1691623</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2092055</t>
+          <t>2099884</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10159,12 +10159,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>30,01%</t>
         </is>
       </c>
     </row>
@@ -10187,12 +10187,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>914545</t>
+          <t>913150</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1690241</t>
+          <t>1667716</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10202,12 +10202,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>49,57%</t>
+          <t>48,91%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10222,12 +10222,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>813826</t>
+          <t>800883</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1079132</t>
+          <t>1078530</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10237,12 +10237,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10257,12 +10257,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1868895</t>
+          <t>1858136</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2633300</t>
+          <t>2708746</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>38,71%</t>
         </is>
       </c>
     </row>
@@ -10300,12 +10300,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>319913</t>
+          <t>316599</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>465238</t>
+          <t>465255</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10315,12 +10315,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>515613</t>
+          <t>515803</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>828571</t>
+          <t>822901</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10350,12 +10350,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>894882</t>
+          <t>890887</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1223001</t>
+          <t>1208023</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10385,12 +10385,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,26%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P71_R2-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P71_R2-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>58913</t>
+          <t>57081</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>90708</t>
+          <t>90220</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>44131</t>
+          <t>44270</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>72221</t>
+          <t>72577</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>107852</t>
+          <t>109729</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>153310</t>
+          <t>153984</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,71%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>232819</t>
+          <t>234468</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>287075</t>
+          <t>288924</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>255432</t>
+          <t>255057</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>315402</t>
+          <t>314733</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>507523</t>
+          <t>505385</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>590494</t>
+          <t>588712</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,67%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>343540</t>
+          <t>339521</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>405148</t>
+          <t>402237</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>39,81%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>392350</t>
+          <t>393499</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>460115</t>
+          <t>457952</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>755202</t>
+          <t>756819</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>844947</t>
+          <t>847100</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>36,93%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>272195</t>
+          <t>273614</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>333262</t>
+          <t>331729</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>482314</t>
+          <t>481911</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>552293</t>
+          <t>549111</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>42,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>771554</t>
+          <t>775483</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>862116</t>
+          <t>867180</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>37,81%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>168027</t>
+          <t>168698</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>220762</t>
+          <t>222828</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>130278</t>
+          <t>129433</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>176321</t>
+          <t>176690</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>312462</t>
+          <t>311563</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>379558</t>
+          <t>381470</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,79%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>610135</t>
+          <t>605285</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>690620</t>
+          <t>682274</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>482417</t>
+          <t>482372</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>556193</t>
+          <t>555629</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1110385</t>
+          <t>1113640</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1219719</t>
+          <t>1215296</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>34,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>37,56%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>553522</t>
+          <t>554393</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>627746</t>
+          <t>630488</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>503754</t>
+          <t>506363</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>580875</t>
+          <t>581703</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,19%</t>
+          <t>37,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1077436</t>
+          <t>1081079</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1191156</t>
+          <t>1194128</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>36,9%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>214094</t>
+          <t>216808</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>272942</t>
+          <t>276715</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>318012</t>
+          <t>317829</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>385215</t>
+          <t>385099</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>552637</t>
+          <t>552467</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>644890</t>
+          <t>640793</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,8%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>159286</t>
+          <t>159443</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>206634</t>
+          <t>202459</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>37,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>113028</t>
+          <t>111676</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>152503</t>
+          <t>151606</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>285920</t>
+          <t>284064</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>343851</t>
+          <t>341093</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>33,56%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>191010</t>
+          <t>191093</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>238220</t>
+          <t>236997</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>43,57%</t>
+          <t>43,35%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>169738</t>
+          <t>169011</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>213299</t>
+          <t>211736</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>45,09%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>374189</t>
+          <t>376536</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>441234</t>
+          <t>440086</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>36,82%</t>
+          <t>37,05%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>43,3%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>95069</t>
+          <t>94533</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>133375</t>
+          <t>132868</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>72743</t>
+          <t>72406</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>108748</t>
+          <t>107371</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>178877</t>
+          <t>177998</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>230806</t>
+          <t>227676</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,4%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27003</t>
+          <t>26020</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>51938</t>
+          <t>51243</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>42708</t>
+          <t>43181</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>72687</t>
+          <t>73259</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>75279</t>
+          <t>76385</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>116377</t>
+          <t>115926</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,41%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>411848</t>
+          <t>409375</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>492353</t>
+          <t>488228</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>304993</t>
+          <t>305740</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>376959</t>
+          <t>375145</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>734965</t>
+          <t>737235</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>841308</t>
+          <t>837968</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,8%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1063806</t>
+          <t>1070872</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1177014</t>
+          <t>1180516</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>940337</t>
+          <t>938744</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1046412</t>
+          <t>1040206</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2044277</t>
+          <t>2046099</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2191729</t>
+          <t>2190088</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>33,46%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1020437</t>
+          <t>1025780</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1134335</t>
+          <t>1130703</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1002253</t>
+          <t>1002160</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1112961</t>
+          <t>1111829</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2052357</t>
+          <t>2058062</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2208030</t>
+          <t>2213543</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>33,82%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>542936</t>
+          <t>539752</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>627470</t>
+          <t>628141</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>873730</t>
+          <t>872523</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>977973</t>
+          <t>974556</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1443179</t>
+          <t>1440326</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1577379</t>
+          <t>1578494</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,11%</t>
         </is>
       </c>
     </row>
@@ -3240,12 +3240,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>62937</t>
+          <t>63513</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>99527</t>
+          <t>98960</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3255,12 +3255,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3275,12 +3275,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>84090</t>
+          <t>84218</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>125008</t>
+          <t>123533</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3310,12 +3310,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>154952</t>
+          <t>157927</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>210158</t>
+          <t>211855</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3325,12 +3325,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,22%</t>
         </is>
       </c>
     </row>
@@ -3353,12 +3353,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>185930</t>
+          <t>187594</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>240985</t>
+          <t>237875</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3388,12 +3388,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>290632</t>
+          <t>288907</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>351762</t>
+          <t>353399</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3423,12 +3423,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>491361</t>
+          <t>494456</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>575690</t>
+          <t>576058</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>25,06%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>254673</t>
+          <t>253025</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>314551</t>
+          <t>311754</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>389094</t>
+          <t>387486</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>457751</t>
+          <t>455906</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>661015</t>
+          <t>658265</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>748884</t>
+          <t>748666</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,57%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>361493</t>
+          <t>367062</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>424807</t>
+          <t>427636</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>44,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>449906</t>
+          <t>448609</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>517913</t>
+          <t>519944</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>39,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>826598</t>
+          <t>825877</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>923018</t>
+          <t>923846</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>35,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>40,19%</t>
         </is>
       </c>
     </row>
@@ -3809,12 +3809,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>225341</t>
+          <t>229079</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>286081</t>
+          <t>289771</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>174580</t>
+          <t>174269</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>229731</t>
+          <t>227161</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>417123</t>
+          <t>419580</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>499922</t>
+          <t>503233</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,57%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>465090</t>
+          <t>463830</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>543966</t>
+          <t>540247</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>381430</t>
+          <t>381469</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>458607</t>
+          <t>457970</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>861836</t>
+          <t>866720</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>971688</t>
+          <t>971397</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,19%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>567097</t>
+          <t>568380</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>651262</t>
+          <t>652868</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>523326</t>
+          <t>524683</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>606866</t>
+          <t>605666</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1122215</t>
+          <t>1119495</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1237280</t>
+          <t>1232426</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>33,22%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>549366</t>
+          <t>548709</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>631463</t>
+          <t>633015</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>526491</t>
+          <t>528772</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>610175</t>
+          <t>611839</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1100815</t>
+          <t>1100754</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1215731</t>
+          <t>1214092</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>32,73%</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4378,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>142746</t>
+          <t>144436</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>188862</t>
+          <t>190315</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>39,74%</t>
+          <t>40,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>127345</t>
+          <t>125830</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>170254</t>
+          <t>169211</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>36,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>285800</t>
+          <t>286244</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>348606</t>
+          <t>344627</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>36,94%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>144747</t>
+          <t>146955</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>186816</t>
+          <t>191003</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>40,19%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>117092</t>
+          <t>117755</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>158793</t>
+          <t>158424</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>272763</t>
+          <t>272143</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>334792</t>
+          <t>335048</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>35,91%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>66914</t>
+          <t>66181</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>100912</t>
+          <t>101445</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>86104</t>
+          <t>87531</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>125452</t>
+          <t>124706</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>163485</t>
+          <t>162487</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>217347</t>
+          <t>215762</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,13%</t>
         </is>
       </c>
     </row>
@@ -4717,12 +4717,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>44713</t>
+          <t>44343</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>74502</t>
+          <t>74713</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>53327</t>
+          <t>52177</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>84871</t>
+          <t>85401</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4767,12 +4767,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>104439</t>
+          <t>104321</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>149917</t>
+          <t>145747</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>15,62%</t>
         </is>
       </c>
     </row>
@@ -4947,12 +4947,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>459194</t>
+          <t>462257</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>549535</t>
+          <t>549653</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4962,12 +4962,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>407897</t>
+          <t>413025</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>490977</t>
+          <t>491423</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4997,12 +4997,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>895086</t>
+          <t>894493</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1012895</t>
+          <t>1011433</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5032,12 +5032,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,57%</t>
         </is>
       </c>
     </row>
@@ -5060,12 +5060,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>832475</t>
+          <t>831216</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>937003</t>
+          <t>940096</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>822890</t>
+          <t>827149</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>931305</t>
+          <t>931033</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1685419</t>
+          <t>1687700</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1832043</t>
+          <t>1833706</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,42%</t>
         </is>
       </c>
     </row>
@@ -5173,12 +5173,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>920732</t>
+          <t>917318</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1034466</t>
+          <t>1027375</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1039922</t>
+          <t>1034157</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1149952</t>
+          <t>1147805</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5223,12 +5223,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1991949</t>
+          <t>1988173</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2150582</t>
+          <t>2143318</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5258,12 +5258,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>30,88%</t>
         </is>
       </c>
     </row>
@@ -5286,12 +5286,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>990155</t>
+          <t>983184</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1104671</t>
+          <t>1096749</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1062824</t>
+          <t>1062463</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1180451</t>
+          <t>1173717</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5336,12 +5336,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2081987</t>
+          <t>2075894</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2236096</t>
+          <t>2237303</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5371,12 +5371,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>32,23%</t>
         </is>
       </c>
     </row>
@@ -5747,12 +5747,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>59209</t>
+          <t>59728</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>91641</t>
+          <t>92797</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5762,12 +5762,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>62722</t>
+          <t>62633</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>99756</t>
+          <t>100667</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5797,12 +5797,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>132246</t>
+          <t>129142</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>182300</t>
+          <t>180863</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5832,12 +5832,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,42%</t>
         </is>
       </c>
     </row>
@@ -5860,12 +5860,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>106513</t>
+          <t>105464</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>146210</t>
+          <t>148221</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5875,12 +5875,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5895,12 +5895,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>146253</t>
+          <t>144135</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>195287</t>
+          <t>194875</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5910,12 +5910,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>259005</t>
+          <t>263598</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>328435</t>
+          <t>329334</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5945,12 +5945,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,97%</t>
         </is>
       </c>
     </row>
@@ -5973,12 +5973,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>169156</t>
+          <t>169607</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>217371</t>
+          <t>216533</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6008,12 +6008,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>218810</t>
+          <t>219379</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>272916</t>
+          <t>274005</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6023,12 +6023,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>403429</t>
+          <t>406847</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>477823</t>
+          <t>477930</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>329806</t>
+          <t>326161</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>384303</t>
+          <t>380249</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>43,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>51,43%</t>
+          <t>50,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>460805</t>
+          <t>459205</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>523781</t>
+          <t>523435</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>46,62%</t>
+          <t>46,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>52,99%</t>
+          <t>52,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>805045</t>
+          <t>803009</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>890663</t>
+          <t>885203</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>46,38%</t>
+          <t>46,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>51,31%</t>
+          <t>51,0%</t>
         </is>
       </c>
     </row>
@@ -6316,12 +6316,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>218906</t>
+          <t>219567</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>277194</t>
+          <t>281013</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6331,12 +6331,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>210558</t>
+          <t>209262</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>269096</t>
+          <t>265929</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6366,12 +6366,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>445791</t>
+          <t>447600</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>528039</t>
+          <t>528646</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,1%</t>
         </is>
       </c>
     </row>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>467478</t>
+          <t>469122</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>547699</t>
+          <t>549168</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>385251</t>
+          <t>385053</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>458778</t>
+          <t>459639</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>879473</t>
+          <t>874227</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>988129</t>
+          <t>986431</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6514,12 +6514,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,44%</t>
         </is>
       </c>
     </row>
@@ -6542,12 +6542,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>555700</t>
+          <t>555078</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>638282</t>
+          <t>641004</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6557,12 +6557,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>592377</t>
+          <t>592335</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>676185</t>
+          <t>676471</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6597,7 +6597,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6612,12 +6612,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1170268</t>
+          <t>1172217</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1286848</t>
+          <t>1290438</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6627,12 +6627,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>31,97%</t>
         </is>
       </c>
     </row>
@@ -6655,12 +6655,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>659751</t>
+          <t>659628</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>751421</t>
+          <t>751159</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6675,7 +6675,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>647347</t>
+          <t>644519</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>731035</t>
+          <t>729920</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1327479</t>
+          <t>1328114</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1459300</t>
+          <t>1452873</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>36,0%</t>
         </is>
       </c>
     </row>
@@ -6885,12 +6885,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>161268</t>
+          <t>159126</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>208629</t>
+          <t>205356</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6900,12 +6900,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>37,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6920,12 +6920,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>147624</t>
+          <t>147383</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>190913</t>
+          <t>193197</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6935,12 +6935,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>35,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6955,12 +6955,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>319044</t>
+          <t>322035</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>384509</t>
+          <t>383047</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6970,12 +6970,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>35,04%</t>
         </is>
       </c>
     </row>
@@ -6998,12 +6998,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>159880</t>
+          <t>163347</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>205415</t>
+          <t>209787</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7013,12 +7013,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>38,49%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7033,12 +7033,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>154876</t>
+          <t>154634</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>198901</t>
+          <t>198686</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7068,12 +7068,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>329804</t>
+          <t>328186</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>390983</t>
+          <t>391680</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7083,12 +7083,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>35,83%</t>
         </is>
       </c>
     </row>
@@ -7111,12 +7111,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>98773</t>
+          <t>99705</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>139272</t>
+          <t>140536</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7126,12 +7126,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7146,12 +7146,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>105999</t>
+          <t>105463</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>147795</t>
+          <t>147751</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7161,12 +7161,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>216560</t>
+          <t>216538</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>272483</t>
+          <t>271309</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>24,82%</t>
         </is>
       </c>
     </row>
@@ -7224,12 +7224,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>44998</t>
+          <t>45120</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>76176</t>
+          <t>74402</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7239,12 +7239,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7259,12 +7259,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>60957</t>
+          <t>60941</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>93692</t>
+          <t>94128</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7279,7 +7279,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7294,12 +7294,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>115871</t>
+          <t>115437</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>159996</t>
+          <t>159988</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7309,7 +7309,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -7454,12 +7454,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>460609</t>
+          <t>463872</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>546080</t>
+          <t>545920</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7469,12 +7469,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7489,12 +7489,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>441665</t>
+          <t>447724</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>525107</t>
+          <t>528294</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7504,12 +7504,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>935336</t>
+          <t>930751</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1054457</t>
+          <t>1054391</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7539,7 +7539,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -7567,12 +7567,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>763793</t>
+          <t>768184</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>870167</t>
+          <t>870755</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7582,12 +7582,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7602,12 +7602,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>715786</t>
+          <t>718015</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>816640</t>
+          <t>818121</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7617,12 +7617,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7637,12 +7637,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1511521</t>
+          <t>1511764</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1650498</t>
+          <t>1655186</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7657,7 +7657,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>24,11%</t>
         </is>
       </c>
     </row>
@@ -7680,12 +7680,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>859451</t>
+          <t>856619</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>963875</t>
+          <t>961432</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7695,12 +7695,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7715,12 +7715,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>951321</t>
+          <t>946617</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1061907</t>
+          <t>1055679</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7730,12 +7730,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7750,12 +7750,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1844533</t>
+          <t>1840852</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1994552</t>
+          <t>1997460</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7765,12 +7765,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>29,1%</t>
         </is>
       </c>
     </row>
@@ -7793,12 +7793,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1062183</t>
+          <t>1061049</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1172666</t>
+          <t>1176044</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7808,12 +7808,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7828,12 +7828,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1197515</t>
+          <t>1201388</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1313839</t>
+          <t>1321203</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7863,12 +7863,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2292824</t>
+          <t>2296136</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2451188</t>
+          <t>2457823</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>33,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>35,8%</t>
         </is>
       </c>
     </row>
@@ -8249,32 +8249,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>88453</t>
+          <t>98003</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>74764</t>
+          <t>82196</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>106853</t>
+          <t>117786</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8284,32 +8284,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>88030</t>
+          <t>95209</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>76148</t>
+          <t>81328</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>102662</t>
+          <t>110295</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8319,32 +8319,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>176483</t>
+          <t>193213</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>156437</t>
+          <t>171750</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>199612</t>
+          <t>217085</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>15,77%</t>
         </is>
       </c>
     </row>
@@ -8362,32 +8362,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>99009</t>
+          <t>103816</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>82698</t>
+          <t>87587</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>115912</t>
+          <t>121390</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8397,32 +8397,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>155034</t>
+          <t>166747</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>139712</t>
+          <t>151910</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>171402</t>
+          <t>186745</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8432,32 +8432,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>254043</t>
+          <t>270563</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>231922</t>
+          <t>246764</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>277287</t>
+          <t>296449</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>21,54%</t>
         </is>
       </c>
     </row>
@@ -8475,32 +8475,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>181945</t>
+          <t>200828</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>162244</t>
+          <t>180029</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>202564</t>
+          <t>221582</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8510,32 +8510,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>297263</t>
+          <t>321357</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>278256</t>
+          <t>300122</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>319930</t>
+          <t>341677</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>39,66%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>43,06%</t>
+          <t>42,16%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8545,32 +8545,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>479208</t>
+          <t>522184</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>451372</t>
+          <t>493074</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>506548</t>
+          <t>551370</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>40,06%</t>
         </is>
       </c>
     </row>
@@ -8588,32 +8588,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>135238</t>
+          <t>163287</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>117461</t>
+          <t>143102</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>154640</t>
+          <t>185261</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8623,32 +8623,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>202715</t>
+          <t>227045</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>184883</t>
+          <t>206853</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>223749</t>
+          <t>247830</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8658,32 +8658,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>337953</t>
+          <t>390332</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>311551</t>
+          <t>363148</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>366728</t>
+          <t>419549</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>30,48%</t>
         </is>
       </c>
     </row>
@@ -8701,17 +8701,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>504645</t>
+          <t>565933</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>504645</t>
+          <t>565933</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>504645</t>
+          <t>565933</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8736,17 +8736,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>743042</t>
+          <t>810359</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>743042</t>
+          <t>810359</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>743042</t>
+          <t>810359</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8771,17 +8771,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1247687</t>
+          <t>1376291</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1247687</t>
+          <t>1376291</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1247687</t>
+          <t>1376291</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8818,32 +8818,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>471445</t>
+          <t>507237</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>304871</t>
+          <t>460271</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>555106</t>
+          <t>551534</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8853,32 +8853,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>621892</t>
+          <t>466122</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>441116</t>
+          <t>430715</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1073178</t>
+          <t>507159</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8888,32 +8888,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1093337</t>
+          <t>973359</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>887270</t>
+          <t>911437</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1706293</t>
+          <t>1036495</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>23,79%</t>
         </is>
       </c>
     </row>
@@ -8931,32 +8931,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>671338</t>
+          <t>704055</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>458582</t>
+          <t>654604</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>775872</t>
+          <t>752743</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8966,32 +8966,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>583585</t>
+          <t>634813</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>425499</t>
+          <t>593344</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>670918</t>
+          <t>671876</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9001,32 +9001,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1254922</t>
+          <t>1338868</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1015411</t>
+          <t>1272962</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1396403</t>
+          <t>1401534</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>32,17%</t>
         </is>
       </c>
     </row>
@@ -9044,32 +9044,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>857341</t>
+          <t>674942</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>664526</t>
+          <t>626041</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1339510</t>
+          <t>723890</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>59,21%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9079,32 +9079,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>617093</t>
+          <t>701810</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>455988</t>
+          <t>661259</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>707809</t>
+          <t>743160</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9114,32 +9114,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1474434</t>
+          <t>1376752</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1229506</t>
+          <t>1314644</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2006585</t>
+          <t>1441852</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
+          <t>31,6%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>30,17%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
           <t>33,09%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>27,59%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>45,03%</t>
         </is>
       </c>
     </row>
@@ -9157,32 +9157,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>262032</t>
+          <t>313193</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>178814</t>
+          <t>277160</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>311258</t>
+          <t>352160</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9192,32 +9192,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>371003</t>
+          <t>354800</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>283945</t>
+          <t>324064</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>577725</t>
+          <t>394914</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9227,32 +9227,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>633035</t>
+          <t>667993</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>518905</t>
+          <t>622083</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>852269</t>
+          <t>722187</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>16,58%</t>
         </is>
       </c>
     </row>
@@ -9270,17 +9270,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2262156</t>
+          <t>2199427</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2262156</t>
+          <t>2199427</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2262156</t>
+          <t>2199427</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9305,17 +9305,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2193572</t>
+          <t>2157546</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2193572</t>
+          <t>2157546</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2193572</t>
+          <t>2157546</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9340,17 +9340,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>4455728</t>
+          <t>4356973</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4455728</t>
+          <t>4356973</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4455728</t>
+          <t>4356973</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9387,32 +9387,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>332998</t>
+          <t>365317</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>305612</t>
+          <t>337754</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>360524</t>
+          <t>395119</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>51,8%</t>
+          <t>51,64%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>47,54%</t>
+          <t>47,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>56,08%</t>
+          <t>55,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9422,32 +9422,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>315306</t>
+          <t>344915</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>292424</t>
+          <t>321886</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>338066</t>
+          <t>367722</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>48,43%</t>
+          <t>47,67%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>44,91%</t>
+          <t>44,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>51,92%</t>
+          <t>50,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9457,32 +9457,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>648304</t>
+          <t>710233</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>611448</t>
+          <t>673314</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>683685</t>
+          <t>747162</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>50,1%</t>
+          <t>49,63%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>47,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>52,84%</t>
+          <t>52,21%</t>
         </is>
       </c>
     </row>
@@ -9500,32 +9500,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>222151</t>
+          <t>236826</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>194823</t>
+          <t>207660</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>252689</t>
+          <t>263553</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>33,47%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9535,32 +9535,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>222712</t>
+          <t>244815</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>202977</t>
+          <t>223124</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>244191</t>
+          <t>268425</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>33,83%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9570,32 +9570,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>444862</t>
+          <t>481641</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>410621</t>
+          <t>445247</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>481844</t>
+          <t>518048</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>36,2%</t>
         </is>
       </c>
     </row>
@@ -9613,32 +9613,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>70541</t>
+          <t>83074</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>54963</t>
+          <t>64986</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>91641</t>
+          <t>105478</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9648,32 +9648,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>79230</t>
+          <t>92128</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>65786</t>
+          <t>77531</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>94823</t>
+          <t>110877</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9683,32 +9683,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>149771</t>
+          <t>175202</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>127478</t>
+          <t>151222</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>174063</t>
+          <t>203684</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>14,23%</t>
         </is>
       </c>
     </row>
@@ -9726,32 +9726,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>17128</t>
+          <t>22260</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9928</t>
+          <t>13656</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29286</t>
+          <t>36574</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9761,32 +9761,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>33851</t>
+          <t>41735</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>25511</t>
+          <t>30519</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>45616</t>
+          <t>55494</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9796,32 +9796,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>50979</t>
+          <t>63995</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>38771</t>
+          <t>49706</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>65834</t>
+          <t>82705</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,78%</t>
         </is>
       </c>
     </row>
@@ -9839,17 +9839,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>642818</t>
+          <t>707477</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>642818</t>
+          <t>707477</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>642818</t>
+          <t>707477</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9874,17 +9874,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>651098</t>
+          <t>723593</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>651098</t>
+          <t>723593</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>651098</t>
+          <t>723593</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9909,17 +9909,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1293916</t>
+          <t>1431070</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1293916</t>
+          <t>1431070</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1293916</t>
+          <t>1431070</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9956,32 +9956,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>892897</t>
+          <t>970557</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>687798</t>
+          <t>914632</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>981554</t>
+          <t>1030632</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9991,32 +9991,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1025228</t>
+          <t>906247</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>852108</t>
+          <t>862148</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1514074</t>
+          <t>952275</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>42,2%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10026,32 +10026,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1918124</t>
+          <t>1876805</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1690106</t>
+          <t>1808325</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2405023</t>
+          <t>1955214</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>27,29%</t>
         </is>
       </c>
     </row>
@@ -10069,32 +10069,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>992497</t>
+          <t>1044697</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>744591</t>
+          <t>987093</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1091345</t>
+          <t>1104608</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10104,32 +10104,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>961330</t>
+          <t>1046375</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>790086</t>
+          <t>1000838</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1045795</t>
+          <t>1102395</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10139,32 +10139,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>1953827</t>
+          <t>2091072</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1691623</t>
+          <t>2012248</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2099884</t>
+          <t>2167444</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>30,25%</t>
         </is>
       </c>
     </row>
@@ -10182,32 +10182,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1109828</t>
+          <t>958843</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>913150</t>
+          <t>897899</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1667716</t>
+          <t>1013334</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10217,32 +10217,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>993586</t>
+          <t>1115295</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>800883</t>
+          <t>1069185</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1078530</t>
+          <t>1168848</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10252,32 +10252,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>2103413</t>
+          <t>2074138</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1858136</t>
+          <t>1996412</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2708746</t>
+          <t>2151710</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>30,03%</t>
         </is>
       </c>
     </row>
@@ -10295,32 +10295,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>414398</t>
+          <t>498739</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>316599</t>
+          <t>450681</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>465255</t>
+          <t>542953</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10330,32 +10330,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>607568</t>
+          <t>623580</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>515803</t>
+          <t>581195</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>822901</t>
+          <t>661527</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10365,32 +10365,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1021966</t>
+          <t>1122320</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>890887</t>
+          <t>1061168</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1208023</t>
+          <t>1183409</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>16,52%</t>
         </is>
       </c>
     </row>
@@ -10408,17 +10408,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3409620</t>
+          <t>3472837</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3409620</t>
+          <t>3472837</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3409620</t>
+          <t>3472837</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10443,17 +10443,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3587712</t>
+          <t>3691497</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3587712</t>
+          <t>3691497</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3587712</t>
+          <t>3691497</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10478,17 +10478,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6997331</t>
+          <t>7164334</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6997331</t>
+          <t>7164334</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6997331</t>
+          <t>7164334</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
